--- a/BE/mgp-service/app/templates/production_template.xlsx
+++ b/BE/mgp-service/app/templates/production_template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10621"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CD0D62-04B3-DA4C-AA14-05203E13CCCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831A2891-D26B-CF48-B6E0-BF3A68B6FF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="34560" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="מסור" sheetId="2" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <definedName name="CLIENT_NAME">[1]ראשי!#REF!</definedName>
     <definedName name="OFFER_DATE">[1]ראשי!#REF!</definedName>
     <definedName name="OFFER_VALID_TO">[1]ראשי!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">מנקבת!$A$1:$J$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">מסור!$A$1:$I$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">מנקבת!$A$1:$S$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">מסור!$A$1:$G$21</definedName>
     <definedName name="prOJECT_NAME">[1]ראשי!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
   <si>
     <t>אורך</t>
   </si>
@@ -112,9 +112,6 @@
     <t>SAW_TABLE_RAILS_DATA_ROW</t>
   </si>
   <si>
-    <t>מיקום ניקוב</t>
-  </si>
-  <si>
     <t>צד הזוית</t>
   </si>
   <si>
@@ -125,6 +122,36 @@
   </si>
   <si>
     <t>PUNCH_TABLE_TRAP_DATA_ROW</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -134,16 +161,9 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -157,66 +177,67 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Heebo"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Heebo"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Heebo"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Heebo"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Heebo"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Heebo"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Heebo"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Heebo"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Heebo"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="16"/>
       <color theme="0"/>
       <name val="Heebo"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="16"/>
+      <color rgb="FF333333"/>
       <name val="Heebo"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF272E2F"/>
-      <name val="Heebo"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="16"/>
       <color rgb="FF8C8C8C"/>
       <name val="Courier New"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
+      <sz val="16"/>
+      <color rgb="FF272E2F"/>
       <name val="Heebo"/>
     </font>
   </fonts>
@@ -240,7 +261,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -276,23 +297,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -316,56 +357,31 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -373,20 +389,39 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -394,7 +429,7 @@
     <xf numFmtId="4" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -402,19 +437,19 @@
     <cellStyle name="Comma 2" xfId="1" xr:uid="{8B711F14-12F9-DB46-A59C-2DE7D2614634}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
+  <dxfs count="38">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
         <color rgb="FF000000"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -433,7 +468,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="16"/>
         <color theme="0"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -459,16 +494,379 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
         <name val="Heebo"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -500,9 +898,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Heebo"/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -518,38 +917,37 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Heebo"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Heebo"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="16"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF272E2F"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
         <name val="Heebo"/>
         <scheme val="none"/>
       </font>
@@ -558,7 +956,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -573,7 +973,7 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="16"/>
         <name val="Heebo"/>
         <scheme val="none"/>
       </font>
@@ -605,7 +1005,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="16"/>
         <color theme="1"/>
         <name val="Heebo"/>
         <scheme val="none"/>
@@ -637,7 +1037,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="16"/>
         <color theme="1"/>
         <name val="Heebo"/>
         <scheme val="none"/>
@@ -664,7 +1064,7 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="16"/>
         <name val="Heebo"/>
         <scheme val="none"/>
       </font>
@@ -695,26 +1095,13 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="16"/>
         <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+        <name val="Heebo"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Heebo"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -737,146 +1124,41 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Heebo"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <name val="Heebo"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Heebo"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Heebo"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Heebo"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -974,41 +1256,6 @@
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF272E2F"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1076,33 +1323,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ACB1EC1-21C6-AF40-A140-308C9117B91F}" name="pricing_table25" displayName="pricing_table25" ref="B10:G16" totalsRowShown="0" headerRowDxfId="26" dataDxfId="11" totalsRowDxfId="23" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5ACB1EC1-21C6-AF40-A140-308C9117B91F}" name="pricing_table25" displayName="pricing_table25" ref="B10:G16" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="35" headerRowBorderDxfId="37" tableBorderDxfId="36" totalsRowBorderDxfId="34">
   <autoFilter ref="B10:G16" xr:uid="{A700047D-2A12-4A24-87A3-5C54C0CD36D6}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9715C0F5-6C58-0C48-A92D-3904FFEE1286}" name="אזור" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{E71665ED-EE05-B544-8402-B3336F34DA2C}" name="שם טרפז" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{58C96AFC-B01E-D446-8E2A-ACF7B2497559}" name="תאור" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{D9DC81BB-9F60-0047-86B9-14278D4E2EE7}" name="אורך" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{B9B74024-7469-A149-9639-A328A6F77916}" name="כמות" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{0FF2A4DA-EE5D-564C-892E-1BAF5895A4E7}" name="אישור" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{FE70B8BE-B7D1-8A4D-976D-722E51C6D2F2}" name="אישור" dataDxfId="27" totalsRowDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{9715C0F5-6C58-0C48-A92D-3904FFEE1286}" name="אזור" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{E71665ED-EE05-B544-8402-B3336F34DA2C}" name="שם טרפז" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{58C96AFC-B01E-D446-8E2A-ACF7B2497559}" name="תאור" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{D9DC81BB-9F60-0047-86B9-14278D4E2EE7}" name="אורך" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{B9B74024-7469-A149-9639-A328A6F77916}" name="כמות" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1856DD68-C283-E64D-A287-74ED308E6FA2}" name="pricing_table255" displayName="pricing_table255" ref="B10:J11" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" totalsRowDxfId="19" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="18">
-  <autoFilter ref="B10:J11" xr:uid="{A700047D-2A12-4A24-87A3-5C54C0CD36D6}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{BAE27508-270F-1640-A00D-5D733FC2839B}" name="אזור" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{FCEFCD78-EA2A-674F-9ED2-FBDD0DA8D442}" name="שם טרפז" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{D5C08E81-8286-534C-BFDC-A6D3A726A839}" name="תאור" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{2AD46FEB-2F64-CB44-AEB9-8BA346D7114A}" name="אורך" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{4091B390-6B52-EC45-9047-7DCFC6E8EA62}" name="כמות" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{66F654BF-BE69-594D-92B9-F2AD452126E6}" name="מיקום ניקוב" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{F599DDE8-C7EC-0142-9BE8-A612F90739F2}" name="צד הזוית" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{25D6A7A9-883C-2E49-94A4-5C8A7E9B159D}" name="קוטר ניקוב" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{36699890-89CE-6A4F-B795-6B84AE3535CD}" name="אישור" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1856DD68-C283-E64D-A287-74ED308E6FA2}" name="pricing_table255" displayName="pricing_table255" ref="B10:S11" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" totalsRowDxfId="31" headerRowBorderDxfId="33" tableBorderDxfId="32" totalsRowBorderDxfId="30">
+  <autoFilter ref="B10:S11" xr:uid="{A700047D-2A12-4A24-87A3-5C54C0CD36D6}"/>
+  <tableColumns count="18">
+    <tableColumn id="20" xr3:uid="{CD781204-8071-D74F-B29B-61F3B8361D3A}" name="אישור" dataDxfId="19" totalsRowDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{BAE27508-270F-1640-A00D-5D733FC2839B}" name="אזור" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{FCEFCD78-EA2A-674F-9ED2-FBDD0DA8D442}" name="שם טרפז" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{D5C08E81-8286-534C-BFDC-A6D3A726A839}" name="תאור" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{2AD46FEB-2F64-CB44-AEB9-8BA346D7114A}" name="אורך" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{4091B390-6B52-EC45-9047-7DCFC6E8EA62}" name="כמות" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{66F654BF-BE69-594D-92B9-F2AD452126E6}" name="1" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{2F66055F-F294-DB49-AB36-AC6CB79FFD15}" name="2" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{7FAB683B-F35F-CC44-8021-FF3C34744A53}" name="3" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{52CA472C-5190-D547-A70B-2E1A86FEB15A}" name="4" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{493B6499-C3D2-FB4C-A846-AD6558CB87B1}" name="5" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{83DE19FA-0E75-C144-9DAD-BC49373A3149}" name="6" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{477B442B-DA6F-B148-9262-DF5D27838422}" name="7" dataDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{82803940-AB6F-D544-8EA8-118B1874FA86}" name="8" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{89407F34-DC6E-9A4A-AD49-7CB84028EBFE}" name="9" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{121AA4DD-F618-7D40-A10F-FB5E4E4018F3}" name="10" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{F599DDE8-C7EC-0142-9BE8-A612F90739F2}" name="צד הזוית" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{25D6A7A9-883C-2E49-94A4-5C8A7E9B159D}" name="קוטר ניקוב" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1430,349 +1686,338 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F0B96F5-D82A-B24D-8E16-7E74024E05A0}">
-  <sheetPr codeName="Sheet5">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:R28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="20" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="26" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="25.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.1640625" style="3"/>
+    <col min="1" max="1" width="2.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" style="3" customWidth="1"/>
+    <col min="6" max="7" width="13.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="25.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="31" x14ac:dyDescent="0.2">
-      <c r="B4" s="22" t="s">
+    <row r="4" spans="2:12" ht="31" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="2:12" ht="23" x14ac:dyDescent="0.2">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="2:12" ht="21" x14ac:dyDescent="0.2">
-      <c r="B6" s="6" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+    </row>
+    <row r="6" spans="2:12" ht="54" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="G6" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="21" x14ac:dyDescent="0.2">
-      <c r="B7" s="9" t="s">
+    <row r="7" spans="2:12" ht="54" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="2:12" ht="23" x14ac:dyDescent="0.2">
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="2:12" ht="3.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="12"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="2:12" s="13" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="18" t="s">
+      <c r="H7" s="13"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+    </row>
+    <row r="9" spans="2:12" ht="3.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="8"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+    </row>
+    <row r="10" spans="2:12" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="D10" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="E10" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="F10" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="G10" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" s="13" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="23" t="s">
+    </row>
+    <row r="11" spans="2:12" s="18" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="B11" s="19"/>
+      <c r="C11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="25"/>
-    </row>
-    <row r="12" spans="2:12" s="13" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="34" t="s">
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="22"/>
+    </row>
+    <row r="12" spans="2:12" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="D12" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="29" t="b">
+      <c r="E12" s="25"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="25"/>
+    </row>
+    <row r="13" spans="2:12" s="18" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="B13" s="27"/>
+      <c r="C13" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="30"/>
+    </row>
+    <row r="14" spans="2:12" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="23" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:12" s="13" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="32"/>
-    </row>
-    <row r="14" spans="2:12" s="13" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="34" t="s">
+      <c r="C14" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="D14" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="29" t="b">
+      <c r="E14" s="25"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="25"/>
+    </row>
+    <row r="15" spans="2:12" s="18" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+      <c r="B15" s="27"/>
+      <c r="C15" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="30"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="23" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:12" s="13" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="32"/>
-    </row>
-    <row r="16" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="34" t="s">
+      <c r="C16" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="D16" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="17"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="31"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
     </row>
     <row r="18" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B19" s="8" t="s">
+      <c r="G18" s="3"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B19" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B20" s="8"/>
-    </row>
-    <row r="21" spans="1:18" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="1"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:18" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="1"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="1"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="1"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B20" s="11"/>
+    </row>
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="2"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+    </row>
+    <row r="22" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+    </row>
+    <row r="23" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="2"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+    </row>
+    <row r="26" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+    </row>
+    <row r="27" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="2"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+    </row>
+    <row r="28" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="2"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1780,11 +2025,11 @@
     <mergeCell ref="C26:I26"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="C28:H28"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B4:G4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.39370078740157483" bottom="0.19685039370078741" header="0.39370078740157483" footer="0"/>
-  <pageSetup paperSize="9" scale="68" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="3.9370078740157501E-2" right="3.9370078740157501E-2" top="0.39370078740157499" bottom="0.196850393700787" header="0.39370078740157499" footer="0"/>
+  <pageSetup paperSize="9" scale="96" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;G</oddHeader>
     <oddFooter>&amp;C&amp;G</oddFooter>
@@ -1798,312 +2043,433 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4F34C7-1DDF-5247-83EC-1DD43634634D}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:R23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="20" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Z23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="26" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="25.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.1640625" style="3"/>
+    <col min="1" max="1" width="2.5" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12" style="2" customWidth="1"/>
+    <col min="3" max="4" width="13.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" style="3" customWidth="1"/>
+    <col min="6" max="7" width="20" style="2" customWidth="1"/>
+    <col min="8" max="17" width="7.33203125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" style="4" customWidth="1"/>
+    <col min="20" max="20" width="16.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.1640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="31" x14ac:dyDescent="0.2">
-      <c r="B4" s="22" t="s">
+    <row r="4" spans="1:26" ht="31" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="7"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="T5" s="7"/>
+    </row>
+    <row r="6" spans="1:26" ht="54" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="54" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="10"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="T8" s="7"/>
+    </row>
+    <row r="9" spans="1:26" ht="3.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="8"/>
+      <c r="T9" s="7"/>
+    </row>
+    <row r="10" spans="1:26" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="O10" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q10" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" s="36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" s="18" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:18" ht="23" x14ac:dyDescent="0.2">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:18" ht="42" x14ac:dyDescent="0.2">
-      <c r="B6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="21" x14ac:dyDescent="0.2">
-      <c r="B7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:18" ht="23" x14ac:dyDescent="0.2">
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" ht="3.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="12"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="27" t="s">
+      <c r="D11" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="17"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+    </row>
+    <row r="12" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="31"/>
+      <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="8" t="s">
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+    </row>
+    <row r="13" spans="1:26" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="15"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B14" s="8" t="s">
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="B15" s="8"/>
-    </row>
-    <row r="16" spans="1:18" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="1"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:18" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="1"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="1"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="1"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+    </row>
+    <row r="16" spans="1:26" s="4" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="2"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+    </row>
+    <row r="17" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+    </row>
+    <row r="18" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="2"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+    </row>
+    <row r="21" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+    </row>
+    <row r="22" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="2"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+    </row>
+    <row r="23" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="2"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="B17:R17"/>
+    <mergeCell ref="C21:R21"/>
+    <mergeCell ref="C22:Q22"/>
+    <mergeCell ref="C23:Q23"/>
+    <mergeCell ref="B4:S4"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="3.937007874015748E-2" right="3.937007874015748E-2" top="0.39370078740157483" bottom="0.19685039370078741" header="0.39370078740157483" footer="0"/>
-  <pageSetup paperSize="9" scale="65" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="3.9370078740157501E-2" right="3.9370078740157501E-2" top="0.39370078740157499" bottom="0.196850393700787" header="0.39370078740157499" footer="0"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;G</oddHeader>
     <oddFooter>&amp;C&amp;G</oddFooter>
